--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89302</v>
+        <v>89308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91916</v>
+        <v>91922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92648</v>
+        <v>92654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92648</v>
+        <v>92654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92654</v>
+        <v>92656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92654</v>
+        <v>92656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92656</v>
+        <v>92174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92656</v>
+        <v>92174</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92174</v>
+        <v>92184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92174</v>
+        <v>92184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92184</v>
+        <v>92186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92184</v>
+        <v>92186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133851094</v>
       </c>
       <c r="B2" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133851029</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>133851004</v>
       </c>
       <c r="B4" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>133850847</v>
       </c>
       <c r="B5" t="n">
-        <v>92187</v>
+        <v>92194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>133850848</v>
       </c>
       <c r="B6" t="n">
-        <v>92187</v>
+        <v>92194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133851094</v>
+        <v>133850847</v>
       </c>
       <c r="B2" t="n">
-        <v>89347</v>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613075</v>
+        <v>613100</v>
       </c>
       <c r="R2" t="n">
-        <v>7149842</v>
+        <v>7149850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-55</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,30 +777,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133851029</v>
+        <v>133850848</v>
       </c>
       <c r="B3" t="n">
-        <v>91987</v>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -808,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612939</v>
+        <v>612937</v>
       </c>
       <c r="R3" t="n">
-        <v>7149788</v>
+        <v>7149821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-45</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133851004</v>
+        <v>133851094</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>89354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613066</v>
+        <v>613075</v>
       </c>
       <c r="R4" t="n">
-        <v>7149832</v>
+        <v>7149842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-67</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133850847</v>
+        <v>133851004</v>
       </c>
       <c r="B5" t="n">
-        <v>92194</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613100</v>
+        <v>613066</v>
       </c>
       <c r="R5" t="n">
-        <v>7149850</v>
+        <v>7149832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-37</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-67</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,108 +1080,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>133850848</v>
-      </c>
-      <c r="B6" t="n">
-        <v>92194</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>67</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sprickporing</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Diplomitoporus crustulinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>612937</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7149821</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50419-2024 artfynd.xlsx
+++ b/artfynd/A 50419-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851094</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>